--- a/source/_static/report/PR_sample_r51.xlsx
+++ b/source/_static/report/PR_sample_r51.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\office\counter\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\siq\github\cop5\source\_static\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF7186A-CEC7-4AC6-9734-3C5CA346C4EE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E6368A-9AB2-4E28-A4B6-00A14A9BDF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PR_sample_r51" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Institution_ID</t>
-  </si>
-  <si>
-    <t>ISNI:1234123412341234</t>
   </si>
   <si>
     <t>Metric_Types</t>
@@ -251,6 +248,9 @@
   <si>
     <t>Unspecified</t>
   </si>
+  <si>
+    <t>P1:1234; ISNI:1234123412341234</t>
+  </si>
 </sst>
 </file>
 
@@ -288,12 +288,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -419,7 +419,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R218"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" style="1" customWidth="1"/>
@@ -476,129 +476,129 @@
         <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E16" s="2">
         <v>17409</v>
@@ -642,16 +642,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" s="2">
         <v>10445</v>
@@ -695,16 +695,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" s="2">
         <v>13058</v>
@@ -748,16 +748,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2">
         <v>7837</v>
@@ -801,16 +801,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2">
         <v>17583</v>
@@ -854,16 +854,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" s="2">
         <v>10550</v>
@@ -907,16 +907,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2">
         <v>13187</v>
@@ -960,16 +960,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="C23" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2">
         <v>7914</v>
@@ -1013,16 +1013,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E24" s="2">
         <v>16642</v>
@@ -1066,16 +1066,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E25" s="2">
         <v>9986</v>
@@ -1119,16 +1119,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E26" s="2">
         <v>12484</v>
@@ -1172,16 +1172,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E27" s="2">
         <v>7491</v>
@@ -1225,16 +1225,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2">
         <v>17181</v>
@@ -1278,16 +1278,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E29" s="2">
         <v>10309</v>
@@ -1331,16 +1331,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" s="2">
         <v>12887</v>
@@ -1384,16 +1384,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E31" s="2">
         <v>7733</v>
@@ -1437,16 +1437,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E32" s="2">
         <v>16373</v>
@@ -1490,16 +1490,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33" s="2">
         <v>9825</v>
@@ -1543,16 +1543,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E34" s="2">
         <v>12283</v>
@@ -1596,16 +1596,16 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E35" s="2">
         <v>7369</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="E36" s="2">
         <v>8189</v>
@@ -1702,16 +1702,16 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2">
         <v>6141</v>
@@ -1755,16 +1755,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E38" s="2">
         <v>16693</v>
@@ -1808,16 +1808,16 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E39" s="2">
         <v>10014</v>
@@ -1861,16 +1861,16 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E40" s="2">
         <v>12520</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E41" s="2">
         <v>7512</v>
@@ -1967,16 +1967,16 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="E42" s="2">
         <v>8352</v>
@@ -2020,16 +2020,16 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E43" s="2">
         <v>6266</v>
@@ -2073,16 +2073,16 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E44" s="2">
         <v>17708</v>
@@ -2126,16 +2126,16 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E45" s="2">
         <v>10625</v>
@@ -2179,16 +2179,16 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E46" s="2">
         <v>13282</v>
@@ -2232,16 +2232,16 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E47" s="2">
         <v>7972</v>
@@ -2285,16 +2285,16 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E48" s="2">
         <v>18473</v>
@@ -2338,16 +2338,16 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E49" s="2">
         <v>11083</v>
@@ -2391,16 +2391,16 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E50" s="2">
         <v>13858</v>
@@ -2444,16 +2444,16 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E51" s="2">
         <v>8314</v>
@@ -2497,16 +2497,16 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E52" s="2">
         <v>17627</v>
@@ -2550,16 +2550,16 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E53" s="2">
         <v>10577</v>
@@ -2603,16 +2603,16 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E54" s="2">
         <v>13222</v>
@@ -2656,16 +2656,16 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E55" s="2">
         <v>7934</v>
@@ -2709,16 +2709,16 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E56" s="2">
         <v>17145</v>
@@ -2762,16 +2762,16 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E57" s="2">
         <v>10288</v>
@@ -2815,16 +2815,16 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E58" s="2">
         <v>12860</v>
@@ -2868,16 +2868,16 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E59" s="2">
         <v>7718</v>
@@ -2921,16 +2921,16 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E60" s="2">
         <v>17617</v>
@@ -2974,16 +2974,16 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E61" s="2">
         <v>10569</v>
@@ -3027,16 +3027,16 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E62" s="2">
         <v>13214</v>
@@ -3080,16 +3080,16 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E63" s="2">
         <v>7929</v>
@@ -3133,16 +3133,16 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E64" s="2">
         <v>18289</v>
@@ -3186,16 +3186,16 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E65" s="2">
         <v>10972</v>
@@ -3239,16 +3239,16 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E66" s="2">
         <v>13719</v>
@@ -3292,16 +3292,16 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E67" s="2">
         <v>8233</v>
@@ -3345,16 +3345,16 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E68" s="2">
         <v>16981</v>
@@ -3398,16 +3398,16 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E69" s="2">
         <v>10189</v>
@@ -3451,16 +3451,16 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E70" s="2">
         <v>12739</v>
@@ -3504,16 +3504,16 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E71" s="2">
         <v>7642</v>
@@ -3557,16 +3557,16 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E72" s="2">
         <v>16987</v>
@@ -3610,16 +3610,16 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E73" s="2">
         <v>10193</v>
@@ -3663,16 +3663,16 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E74" s="2">
         <v>12742</v>
@@ -3716,16 +3716,16 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E75" s="2">
         <v>7645</v>
@@ -3769,16 +3769,16 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E76" s="2">
         <v>17713</v>
@@ -3822,16 +3822,16 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E77" s="2">
         <v>10628</v>
@@ -3875,16 +3875,16 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E78" s="2">
         <v>13287</v>
@@ -3928,16 +3928,16 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E79" s="2">
         <v>7974</v>
@@ -3981,16 +3981,16 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E80" s="2">
         <v>19231</v>
@@ -4034,16 +4034,16 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E81" s="2">
         <v>11537</v>
@@ -4087,16 +4087,16 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E82" s="2">
         <v>14424</v>
@@ -4140,16 +4140,16 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E83" s="2">
         <v>8654</v>
@@ -4193,16 +4193,16 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C84" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E84" s="2">
         <v>17665</v>
@@ -4246,16 +4246,16 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E85" s="2">
         <v>10599</v>
@@ -4299,16 +4299,16 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E86" s="2">
         <v>13251</v>
@@ -4352,16 +4352,16 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E87" s="2">
         <v>7949</v>
@@ -4405,16 +4405,16 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E88" s="2">
         <v>18798</v>
@@ -4458,16 +4458,16 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E89" s="2">
         <v>11279</v>
@@ -4511,16 +4511,16 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E90" s="2">
         <v>14100</v>
@@ -4564,16 +4564,16 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E91" s="2">
         <v>8459</v>
@@ -4617,16 +4617,16 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C92" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E92" s="2">
         <v>19421</v>
@@ -4670,16 +4670,16 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E93" s="2">
         <v>11653</v>
@@ -4723,16 +4723,16 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E94" s="2">
         <v>14568</v>
@@ -4776,16 +4776,16 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E95" s="2">
         <v>8742</v>
@@ -4829,16 +4829,16 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E96" s="2">
         <v>18161</v>
@@ -4882,16 +4882,16 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E97" s="2">
         <v>10897</v>
@@ -4935,16 +4935,16 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E98" s="2">
         <v>13622</v>
@@ -4988,16 +4988,16 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E99" s="2">
         <v>8173</v>
@@ -5041,16 +5041,16 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E100" s="2">
         <v>16853</v>
@@ -5094,16 +5094,16 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E101" s="2">
         <v>10111</v>
@@ -5147,16 +5147,16 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E102" s="2">
         <v>12640</v>
@@ -5200,16 +5200,16 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E103" s="2">
         <v>7585</v>
@@ -5253,16 +5253,16 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E104" s="2">
         <v>19121</v>
@@ -5306,16 +5306,16 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E105" s="2">
         <v>11472</v>
@@ -5359,16 +5359,16 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E106" s="2">
         <v>14343</v>
@@ -5412,16 +5412,16 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E107" s="2">
         <v>8605</v>
@@ -5465,16 +5465,16 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C108" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E108" s="2">
         <v>19546</v>
@@ -5518,16 +5518,16 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E109" s="2">
         <v>11727</v>
@@ -5571,16 +5571,16 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E110" s="2">
         <v>14658</v>
@@ -5624,16 +5624,16 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E111" s="2">
         <v>8796</v>
@@ -5677,16 +5677,16 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E112" s="2">
         <v>19218</v>
@@ -5730,16 +5730,16 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E113" s="2">
         <v>11531</v>
@@ -5783,16 +5783,16 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E114" s="2">
         <v>14415</v>
@@ -5836,16 +5836,16 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E115" s="2">
         <v>8649</v>
@@ -5889,16 +5889,16 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E116" s="2">
         <v>16767</v>
@@ -5942,16 +5942,16 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E117" s="2">
         <v>10060</v>
@@ -5995,16 +5995,16 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E118" s="2">
         <v>12576</v>
@@ -6048,16 +6048,16 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E119" s="2">
         <v>7545</v>
@@ -6101,16 +6101,16 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E120" s="2">
         <v>16677</v>
@@ -6154,16 +6154,16 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E121" s="2">
         <v>10006</v>
@@ -6207,16 +6207,16 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E122" s="2">
         <v>12510</v>
@@ -6260,16 +6260,16 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E123" s="2">
         <v>7506</v>
@@ -6313,16 +6313,16 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C124" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E124" s="2">
         <v>17395</v>
@@ -6366,16 +6366,16 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E125" s="2">
         <v>10437</v>
@@ -6419,16 +6419,16 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E126" s="2">
         <v>13048</v>
@@ -6472,16 +6472,16 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E127" s="2">
         <v>7829</v>
@@ -6525,16 +6525,16 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E128" s="2">
         <v>17209</v>
@@ -6578,16 +6578,16 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E129" s="2">
         <v>10326</v>
@@ -6631,16 +6631,16 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E130" s="2">
         <v>12908</v>
@@ -6684,16 +6684,16 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E131" s="2">
         <v>7747</v>
@@ -6737,16 +6737,16 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C132" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E132" s="2">
         <v>17922</v>
@@ -6790,16 +6790,16 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E133" s="2">
         <v>10752</v>
@@ -6843,16 +6843,16 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E134" s="2">
         <v>13442</v>
@@ -6896,16 +6896,16 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E135" s="2">
         <v>8066</v>
@@ -6949,16 +6949,16 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E136" s="2">
         <v>17135</v>
@@ -7002,16 +7002,16 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E137" s="2">
         <v>10281</v>
@@ -7055,16 +7055,16 @@
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E138" s="2">
         <v>12853</v>
@@ -7108,16 +7108,16 @@
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E139" s="2">
         <v>7712</v>
@@ -7161,16 +7161,16 @@
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E140" s="2">
         <v>17958</v>
@@ -7214,16 +7214,16 @@
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E141" s="2">
         <v>10774</v>
@@ -7267,16 +7267,16 @@
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E142" s="2">
         <v>13470</v>
@@ -7320,16 +7320,16 @@
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E143" s="2">
         <v>8081</v>
@@ -7373,16 +7373,16 @@
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E144" s="2">
         <v>15659</v>
@@ -7426,16 +7426,16 @@
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E145" s="2">
         <v>9396</v>
@@ -7479,16 +7479,16 @@
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E146" s="2">
         <v>11746</v>
@@ -7532,16 +7532,16 @@
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E147" s="2">
         <v>7050</v>
@@ -7585,16 +7585,16 @@
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E148" s="2">
         <v>196697</v>
@@ -7638,16 +7638,16 @@
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E149" s="2">
         <v>195375</v>
@@ -7691,16 +7691,16 @@
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C150" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E150" s="2">
         <v>16215</v>
@@ -7744,16 +7744,16 @@
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E151" s="2">
         <v>9729</v>
@@ -7797,16 +7797,16 @@
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E152" s="2">
         <v>12161</v>
@@ -7850,16 +7850,16 @@
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E153" s="2">
         <v>7298</v>
@@ -7903,16 +7903,16 @@
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E154" s="2">
         <v>18872</v>
@@ -7956,16 +7956,16 @@
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E155" s="2">
         <v>11324</v>
@@ -8009,16 +8009,16 @@
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E156" s="2">
         <v>14157</v>
@@ -8062,16 +8062,16 @@
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E157" s="2">
         <v>8495</v>
@@ -8115,16 +8115,16 @@
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C158" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E158" s="2">
         <v>15523</v>
@@ -8168,16 +8168,16 @@
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E159" s="2">
         <v>9314</v>
@@ -8221,16 +8221,16 @@
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E160" s="2">
         <v>11643</v>
@@ -8274,16 +8274,16 @@
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E161" s="2">
         <v>7098</v>
@@ -8327,16 +8327,16 @@
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E162" s="2">
         <v>3672</v>
@@ -8380,16 +8380,16 @@
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E163" s="2">
         <v>2757</v>
@@ -8433,16 +8433,16 @@
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E164" s="2">
         <v>19634</v>
@@ -8486,16 +8486,16 @@
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E165" s="2">
         <v>11779</v>
@@ -8539,16 +8539,16 @@
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E166" s="2">
         <v>14394</v>
@@ -8592,16 +8592,16 @@
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E167" s="2">
         <v>10600</v>
@@ -8645,16 +8645,16 @@
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E168" s="2">
         <v>10148</v>
@@ -8698,16 +8698,16 @@
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E169" s="2">
         <v>8280</v>
@@ -8751,16 +8751,16 @@
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C170" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E170" s="2">
         <v>19254</v>
@@ -8804,16 +8804,16 @@
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E171" s="2">
         <v>11553</v>
@@ -8857,16 +8857,16 @@
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E172" s="2">
         <v>14442</v>
@@ -8910,16 +8910,16 @@
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E173" s="2">
         <v>8666</v>
@@ -8963,16 +8963,16 @@
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E174" s="2">
         <v>16789</v>
@@ -9016,16 +9016,16 @@
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E175" s="2">
         <v>10073</v>
@@ -9069,16 +9069,16 @@
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E176" s="2">
         <v>12592</v>
@@ -9122,16 +9122,16 @@
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E177" s="2">
         <v>7555</v>
@@ -9175,16 +9175,16 @@
     </row>
     <row r="178" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C178" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E178" s="2">
         <v>18050</v>
@@ -9228,16 +9228,16 @@
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E179" s="2">
         <v>10829</v>
@@ -9281,16 +9281,16 @@
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E180" s="2">
         <v>13538</v>
@@ -9334,16 +9334,16 @@
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E181" s="2">
         <v>8123</v>
@@ -9387,16 +9387,16 @@
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E182" s="2">
         <v>19021</v>
@@ -9440,16 +9440,16 @@
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E183" s="2">
         <v>11413</v>
@@ -9493,16 +9493,16 @@
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E184" s="2">
         <v>14268</v>
@@ -9546,16 +9546,16 @@
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E185" s="2">
         <v>8560</v>
@@ -9599,16 +9599,16 @@
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C186" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E186" s="2">
         <v>18451</v>
@@ -9652,16 +9652,16 @@
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E187" s="2">
         <v>11072</v>
@@ -9705,16 +9705,16 @@
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E188" s="2">
         <v>13841</v>
@@ -9758,16 +9758,16 @@
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E189" s="2">
         <v>8304</v>
@@ -9811,16 +9811,16 @@
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E190" s="2">
         <v>16518</v>
@@ -9864,16 +9864,16 @@
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E191" s="2">
         <v>9908</v>
@@ -9917,16 +9917,16 @@
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E192" s="2">
         <v>12389</v>
@@ -9970,16 +9970,16 @@
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E193" s="2">
         <v>7432</v>
@@ -10023,16 +10023,16 @@
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C194" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E194" s="2">
         <v>17783</v>
@@ -10076,16 +10076,16 @@
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E195" s="2">
         <v>10670</v>
@@ -10129,16 +10129,16 @@
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E196" s="2">
         <v>13337</v>
@@ -10182,16 +10182,16 @@
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E197" s="2">
         <v>8003</v>
@@ -10235,16 +10235,16 @@
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E198" s="2">
         <v>19015</v>
@@ -10288,16 +10288,16 @@
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E199" s="2">
         <v>11411</v>
@@ -10341,16 +10341,16 @@
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E200" s="2">
         <v>14264</v>
@@ -10394,16 +10394,16 @@
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E201" s="2">
         <v>8560</v>
@@ -10447,16 +10447,16 @@
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C202" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E202" s="2">
         <v>19812</v>
@@ -10500,16 +10500,16 @@
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E203" s="2">
         <v>11888</v>
@@ -10553,16 +10553,16 @@
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E204" s="2">
         <v>14862</v>
@@ -10606,16 +10606,16 @@
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E205" s="2">
         <v>8919</v>
@@ -10659,16 +10659,16 @@
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E206" s="2">
         <v>16809</v>
@@ -10712,16 +10712,16 @@
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E207" s="2">
         <v>10087</v>
@@ -10765,16 +10765,16 @@
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E208" s="2">
         <v>12609</v>
@@ -10818,16 +10818,16 @@
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E209" s="2">
         <v>7565</v>
@@ -10871,16 +10871,16 @@
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C210" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E210" s="2">
         <v>17882</v>
@@ -10924,16 +10924,16 @@
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E211" s="2">
         <v>10730</v>
@@ -10977,16 +10977,16 @@
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E212" s="2">
         <v>13413</v>
@@ -11030,16 +11030,16 @@
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E213" s="2">
         <v>8050</v>
@@ -11083,16 +11083,16 @@
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E214" s="2">
         <v>19470</v>
@@ -11136,16 +11136,16 @@
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E215" s="2">
         <v>11682</v>
@@ -11189,16 +11189,16 @@
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E216" s="2">
         <v>14604</v>
@@ -11242,16 +11242,16 @@
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E217" s="2">
         <v>8761</v>
